--- a/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
+++ b/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
+++ b/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
+++ b/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
+++ b/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>FRLMPredictableAdverseDrugReaction.entry</t>
   </si>
   <si>
-    <t>Entrées</t>
+    <t>Modèles logiques contenus dans la section</t>
   </si>
   <si>
     <t>FRLMSection.entry</t>
@@ -375,7 +375,7 @@
 </t>
   </si>
   <si>
-    <t>Entrée Effet indesirable</t>
+    <t>Effet indésirable</t>
   </si>
 </sst>
 </file>

--- a/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
+++ b/main/ig/StructureDefinition-FRLMPredictableAdverseDrugReaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
